--- a/data/Taller_DET_Agosto/Carga_ob/elmo_data.xlsx
+++ b/data/Taller_DET_Agosto/Carga_ob/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Taller_DET_Agosto\Carga_ob\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Taller_DET_Agosto\Carga_ob\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18FED606-10CA-4460-8594-DE7D29EE8BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7E634C-A78F-4B3B-A416-9984B201631C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -1477,38 +1477,38 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="5" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="6" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="6" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2308,6 +2308,9 @@
       <c r="AC9">
         <v>8</v>
       </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2319,16 +2322,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2354,7 +2357,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2380,7 +2383,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -2388,7 +2391,8 @@
         <v>59</v>
       </c>
       <c r="C3" s="8">
-        <v>35722</v>
+        <f>2*35722</f>
+        <v>71444</v>
       </c>
       <c r="D3" s="12">
         <v>38221</v>
@@ -2397,7 +2401,7 @@
         <v>5733</v>
       </c>
       <c r="F3" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G3" s="8">
         <v>1</v>
@@ -2416,14 +2420,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2443,7 +2447,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2463,7 +2467,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -2494,17 +2498,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H236"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2530,7 +2534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2556,7 +2560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2582,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2608,7 +2612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2634,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2660,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2686,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2712,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2738,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2764,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2790,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2816,7 +2820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2842,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2868,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2894,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2920,7 +2924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2946,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2972,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2998,7 +3002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3024,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3050,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3076,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3102,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3128,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3154,7 +3158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3180,7 +3184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3206,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3232,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3258,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3284,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3310,7 +3314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3336,7 +3340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3362,7 +3366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3388,7 +3392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3414,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3440,7 +3444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3466,7 +3470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3492,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3518,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3544,7 +3548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3570,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3596,7 +3600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3622,7 +3626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3648,7 +3652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3674,7 +3678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3700,7 +3704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3726,7 +3730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3752,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3778,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3804,7 +3808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>49</v>
       </c>
@@ -3830,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>50</v>
       </c>
@@ -3856,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>51</v>
       </c>
@@ -3882,7 +3886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>52</v>
       </c>
@@ -3908,7 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>53</v>
       </c>
@@ -3934,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>54</v>
       </c>
@@ -3960,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
@@ -3986,7 +3990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4012,7 +4016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4038,7 +4042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>58</v>
       </c>
@@ -4064,7 +4068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>59</v>
       </c>
@@ -4090,7 +4094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60</v>
       </c>
@@ -4116,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>61</v>
       </c>
@@ -4142,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>62</v>
       </c>
@@ -4168,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>63</v>
       </c>
@@ -4194,7 +4198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>64</v>
       </c>
@@ -4220,7 +4224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>65</v>
       </c>
@@ -4246,7 +4250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>66</v>
       </c>
@@ -4272,7 +4276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>67</v>
       </c>
@@ -4298,7 +4302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>68</v>
       </c>
@@ -4324,7 +4328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>69</v>
       </c>
@@ -4350,7 +4354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>70</v>
       </c>
@@ -4376,7 +4380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>71</v>
       </c>
@@ -4402,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>72</v>
       </c>
@@ -4428,7 +4432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>73</v>
       </c>
@@ -4454,7 +4458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>74</v>
       </c>
@@ -4480,7 +4484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>75</v>
       </c>
@@ -4506,7 +4510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>76</v>
       </c>
@@ -4532,7 +4536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>77</v>
       </c>
@@ -4558,7 +4562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>78</v>
       </c>
@@ -4584,7 +4588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>79</v>
       </c>
@@ -4610,7 +4614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>80</v>
       </c>
@@ -4636,7 +4640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>81</v>
       </c>
@@ -4662,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>82</v>
       </c>
@@ -4688,7 +4692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>83</v>
       </c>
@@ -4714,7 +4718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>84</v>
       </c>
@@ -4740,7 +4744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>85</v>
       </c>
@@ -4766,7 +4770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>86</v>
       </c>
@@ -4792,7 +4796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>87</v>
       </c>
@@ -4818,7 +4822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>88</v>
       </c>
@@ -4844,7 +4848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>89</v>
       </c>
@@ -4870,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>90</v>
       </c>
@@ -4896,7 +4900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>91</v>
       </c>
@@ -4922,7 +4926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>92</v>
       </c>
@@ -4948,7 +4952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>93</v>
       </c>
@@ -4974,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>94</v>
       </c>
@@ -5000,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>95</v>
       </c>
@@ -5026,7 +5030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>96</v>
       </c>
@@ -5052,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>97</v>
       </c>
@@ -5078,7 +5082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>98</v>
       </c>
@@ -5104,7 +5108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>99</v>
       </c>
@@ -5130,7 +5134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>100</v>
       </c>
@@ -5156,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>101</v>
       </c>
@@ -5182,7 +5186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>102</v>
       </c>
@@ -5208,7 +5212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>103</v>
       </c>
@@ -5234,7 +5238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>104</v>
       </c>
@@ -5260,7 +5264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>105</v>
       </c>
@@ -5286,7 +5290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>106</v>
       </c>
@@ -5312,7 +5316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>107</v>
       </c>
@@ -5338,7 +5342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>108</v>
       </c>
@@ -5364,7 +5368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>109</v>
       </c>
@@ -5390,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>110</v>
       </c>
@@ -5416,7 +5420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>111</v>
       </c>
@@ -5442,7 +5446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>112</v>
       </c>
@@ -5468,7 +5472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>113</v>
       </c>
@@ -5494,7 +5498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>114</v>
       </c>
@@ -5520,7 +5524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>115</v>
       </c>
@@ -5546,7 +5550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>116</v>
       </c>
@@ -5572,7 +5576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>117</v>
       </c>
@@ -5598,7 +5602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>118</v>
       </c>
@@ -5624,7 +5628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>119</v>
       </c>
@@ -5650,7 +5654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>120</v>
       </c>
@@ -5676,7 +5680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>121</v>
       </c>
@@ -5702,7 +5706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>122</v>
       </c>
@@ -5728,7 +5732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>123</v>
       </c>
@@ -5754,7 +5758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>124</v>
       </c>
@@ -5780,7 +5784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>125</v>
       </c>
@@ -5806,7 +5810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>126</v>
       </c>
@@ -5832,7 +5836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>127</v>
       </c>
@@ -5858,7 +5862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>128</v>
       </c>
@@ -5884,7 +5888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>129</v>
       </c>
@@ -5910,7 +5914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>130</v>
       </c>
@@ -5936,7 +5940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>131</v>
       </c>
@@ -5962,7 +5966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>132</v>
       </c>
@@ -5988,7 +5992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>133</v>
       </c>
@@ -6014,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>134</v>
       </c>
@@ -6040,7 +6044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>135</v>
       </c>
@@ -6066,7 +6070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>136</v>
       </c>
@@ -6092,7 +6096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>137</v>
       </c>
@@ -6118,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>138</v>
       </c>
@@ -6144,7 +6148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>139</v>
       </c>
@@ -6170,7 +6174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>140</v>
       </c>
@@ -6196,7 +6200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>141</v>
       </c>
@@ -6222,7 +6226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>142</v>
       </c>
@@ -6248,7 +6252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>143</v>
       </c>
@@ -6274,7 +6278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>144</v>
       </c>
@@ -6300,7 +6304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>145</v>
       </c>
@@ -6326,7 +6330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>146</v>
       </c>
@@ -6352,7 +6356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>147</v>
       </c>
@@ -6378,7 +6382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>148</v>
       </c>
@@ -6404,7 +6408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>149</v>
       </c>
@@ -6430,7 +6434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>150</v>
       </c>
@@ -6456,7 +6460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>151</v>
       </c>
@@ -6482,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>152</v>
       </c>
@@ -6508,7 +6512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>153</v>
       </c>
@@ -6534,7 +6538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>154</v>
       </c>
@@ -6560,7 +6564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>155</v>
       </c>
@@ -6586,7 +6590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>156</v>
       </c>
@@ -6612,7 +6616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>157</v>
       </c>
@@ -6638,7 +6642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>158</v>
       </c>
@@ -6664,7 +6668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>159</v>
       </c>
@@ -6690,7 +6694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>160</v>
       </c>
@@ -6716,7 +6720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>161</v>
       </c>
@@ -6742,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>162</v>
       </c>
@@ -6768,7 +6772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>163</v>
       </c>
@@ -6794,7 +6798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>164</v>
       </c>
@@ -6820,7 +6824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>165</v>
       </c>
@@ -6846,7 +6850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>166</v>
       </c>
@@ -6872,7 +6876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>167</v>
       </c>
@@ -6898,7 +6902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>168</v>
       </c>
@@ -6924,7 +6928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>169</v>
       </c>
@@ -6950,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>170</v>
       </c>
@@ -6976,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>171</v>
       </c>
@@ -7002,7 +7006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>172</v>
       </c>
@@ -7028,7 +7032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>173</v>
       </c>
@@ -7054,7 +7058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>174</v>
       </c>
@@ -7080,7 +7084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>175</v>
       </c>
@@ -7106,7 +7110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>176</v>
       </c>
@@ -7132,7 +7136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>177</v>
       </c>
@@ -7158,7 +7162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>178</v>
       </c>
@@ -7184,7 +7188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>179</v>
       </c>
@@ -7210,7 +7214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>180</v>
       </c>
@@ -7236,7 +7240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>181</v>
       </c>
@@ -7262,7 +7266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>182</v>
       </c>
@@ -7288,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>183</v>
       </c>
@@ -7314,7 +7318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>184</v>
       </c>
@@ -7340,7 +7344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>185</v>
       </c>
@@ -7366,7 +7370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>186</v>
       </c>
@@ -7392,7 +7396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>187</v>
       </c>
@@ -7418,7 +7422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>188</v>
       </c>
@@ -7444,7 +7448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>189</v>
       </c>
@@ -7470,7 +7474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>190</v>
       </c>
@@ -7496,7 +7500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>191</v>
       </c>
@@ -7522,7 +7526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>192</v>
       </c>
@@ -7548,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>193</v>
       </c>
@@ -7574,7 +7578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
@@ -7600,7 +7604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>195</v>
       </c>
@@ -7626,7 +7630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>196</v>
       </c>
@@ -7652,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>197</v>
       </c>
@@ -7678,7 +7682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>198</v>
       </c>
@@ -7704,7 +7708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>199</v>
       </c>
@@ -7730,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>200</v>
       </c>
@@ -7756,7 +7760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>201</v>
       </c>
@@ -7782,7 +7786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>202</v>
       </c>
@@ -7808,7 +7812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>203</v>
       </c>
@@ -7834,7 +7838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>204</v>
       </c>
@@ -7860,7 +7864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>205</v>
       </c>
@@ -7886,7 +7890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>206</v>
       </c>
@@ -7912,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>207</v>
       </c>
@@ -7938,7 +7942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>208</v>
       </c>
@@ -7964,7 +7968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>209</v>
       </c>
@@ -7990,7 +7994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>210</v>
       </c>
@@ -8016,90 +8020,90 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213"/>
       <c r="C213"/>
       <c r="D213"/>
       <c r="G213"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214"/>
       <c r="C214"/>
       <c r="D214"/>
       <c r="G214"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215"/>
       <c r="C215"/>
       <c r="D215"/>
       <c r="G215"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216"/>
       <c r="C216"/>
       <c r="D216"/>
       <c r="G216"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217"/>
       <c r="C217"/>
       <c r="D217"/>
       <c r="G217"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218"/>
       <c r="C218"/>
       <c r="D218"/>
       <c r="G218"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219"/>
       <c r="C219"/>
       <c r="D219"/>
       <c r="G219"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220"/>
       <c r="C220"/>
       <c r="D220"/>
       <c r="G220"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221"/>
       <c r="C221"/>
       <c r="D221"/>
       <c r="G221"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222"/>
       <c r="C222"/>
       <c r="D222"/>
       <c r="G222"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223"/>
       <c r="C223"/>
       <c r="D223"/>
       <c r="G223"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224"/>
       <c r="C224"/>
       <c r="D224"/>
       <c r="G224"/>
     </row>
-    <row r="225" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="226" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="227" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="228" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="229" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="230" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="231" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="232" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="233" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="234" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="235" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="236" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="225" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="226" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="227" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="228" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="229" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="230" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="231" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="232" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="233" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="234" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="235" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="236" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8112,14 +8116,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -8130,7 +8134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -8141,7 +8145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8152,7 +8156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -8163,7 +8167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -8174,7 +8178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -8185,7 +8189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -8196,7 +8200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>11</v>
       </c>
@@ -8207,7 +8211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>12</v>
       </c>
@@ -8218,7 +8222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>14</v>
       </c>
@@ -8229,7 +8233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>15</v>
       </c>
@@ -8240,7 +8244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>16</v>
       </c>

--- a/data/Taller_DET_Agosto/Carga_ob/elmo_data.xlsx
+++ b/data/Taller_DET_Agosto/Carga_ob/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Taller_DET_Agosto\Carga_ob\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7E634C-A78F-4B3B-A416-9984B201631C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C55ED14-FAE4-40DE-9C1F-5BF49C892AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2401,7 +2401,7 @@
         <v>5733</v>
       </c>
       <c r="F3" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G3" s="8">
         <v>1</v>
